--- a/data/trans_dic/IQ23_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que duermen las horas recomendadas en función de su edad</t>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,49; 84,47</t>
+          <t>66,64; 84,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,18; 64,22</t>
+          <t>43,19; 64,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,66; 70,22</t>
+          <t>49,63; 69,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,66; 86,57</t>
+          <t>69,44; 86,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,08; 90,66</t>
+          <t>74,4; 90,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,12; 69,28</t>
+          <t>49,71; 69,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,18; 67,8</t>
+          <t>46,78; 67,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,38; 80,52</t>
+          <t>61,89; 79,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,77; 85,85</t>
+          <t>73,61; 86,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,33; 63,51</t>
+          <t>49,66; 64,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51,22; 66,07</t>
+          <t>51,43; 66,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,24; 81,19</t>
+          <t>68,85; 82,13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,92; 65,74</t>
+          <t>49,96; 65,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,7; 77,01</t>
+          <t>61,06; 76,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,7; 62,71</t>
+          <t>46,78; 63,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,42; 90,49</t>
+          <t>70,76; 90,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,44; 74,44</t>
+          <t>60,29; 74,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,2; 79,78</t>
+          <t>66,46; 80,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,75; 66,06</t>
+          <t>49,34; 65,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,26; 76,12</t>
+          <t>59,56; 75,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,82; 68,57</t>
+          <t>57,84; 68,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65,98; 76,61</t>
+          <t>66,76; 76,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,07; 62,03</t>
+          <t>50,79; 62,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,76; 81,66</t>
+          <t>67,42; 82,27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,17; 89,95</t>
+          <t>74,13; 89,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,98; 90,63</t>
+          <t>76,42; 90,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,17; 64,77</t>
+          <t>44,58; 65,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,93; 65,99</t>
+          <t>45,98; 66,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,39; 85,66</t>
+          <t>70,39; 85,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,19; 84,46</t>
+          <t>67,96; 84,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,37; 67,75</t>
+          <t>49,03; 67,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,18; 71,38</t>
+          <t>51,91; 70,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75,54; 85,69</t>
+          <t>74,86; 85,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,34; 85,74</t>
+          <t>75,47; 86,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,68; 64,65</t>
+          <t>49,91; 64,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,48; 65,49</t>
+          <t>52,23; 65,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,79; 90,57</t>
+          <t>76,52; 89,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,55; 80,46</t>
+          <t>63,62; 80,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,37; 79,29</t>
+          <t>62,65; 79,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,95; 86,01</t>
+          <t>68,01; 85,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,62; 88,01</t>
+          <t>73,25; 88,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,33; 82,36</t>
+          <t>65,26; 81,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,16; 74,29</t>
+          <t>56,64; 74,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,37; 87,81</t>
+          <t>64,56; 86,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,12; 87,57</t>
+          <t>77,76; 87,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,4; 78,77</t>
+          <t>67,29; 79,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,68; 74,73</t>
+          <t>62,41; 74,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,71; 83,85</t>
+          <t>69,46; 83,82</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,62; 82,68</t>
+          <t>61,15; 82,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,89; 67,62</t>
+          <t>44,34; 70,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,58; 93,23</t>
+          <t>75,5; 92,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,5; 84,07</t>
+          <t>64,09; 84,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,55; 76,81</t>
+          <t>53,5; 76,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,2; 71,62</t>
+          <t>47,62; 71,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,6; 91,74</t>
+          <t>74,4; 91,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>75,83; 91,33</t>
+          <t>75,63; 91,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,35; 75,94</t>
+          <t>60,89; 77,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,36; 67,54</t>
+          <t>50,01; 67,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,21; 90,18</t>
+          <t>77,46; 90,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,8; 86,76</t>
+          <t>73,39; 85,84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,76; 91,31</t>
+          <t>74,07; 90,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,39; 89,9</t>
+          <t>74,13; 90,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,09; 79,19</t>
+          <t>58,31; 78,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,27; 71,88</t>
+          <t>51,16; 72,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75,24; 90,56</t>
+          <t>75,56; 90,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,72; 79,8</t>
+          <t>60,4; 80,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,26; 80,76</t>
+          <t>61,2; 80,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,23; 63,46</t>
+          <t>41,98; 63,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77,9; 88,83</t>
+          <t>77,52; 88,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,71; 82,57</t>
+          <t>69,66; 83,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63,28; 76,94</t>
+          <t>62,82; 77,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,14; 64,49</t>
+          <t>48,36; 64,43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,21; 83,47</t>
+          <t>71,3; 83,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,07; 82,39</t>
+          <t>70,91; 82,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,92; 77,18</t>
+          <t>64,28; 76,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,22; 58,61</t>
+          <t>42,98; 58,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,62; 81,43</t>
+          <t>68,29; 80,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,78; 80,35</t>
+          <t>67,85; 80,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,48; 71,56</t>
+          <t>59,29; 72,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,94; 63,84</t>
+          <t>47,04; 64,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,3; 80,78</t>
+          <t>71,94; 80,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70,98; 79,62</t>
+          <t>70,94; 79,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63,75; 72,6</t>
+          <t>63,75; 72,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,69; 59,68</t>
+          <t>47,47; 59,92</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,27; 71,44</t>
+          <t>59,45; 71,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,22; 75,44</t>
+          <t>64,29; 75,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,99; 82,99</t>
+          <t>73,13; 83,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77,52; 88,16</t>
+          <t>77,69; 88,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,48; 72,03</t>
+          <t>60,44; 72,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,91; 77,64</t>
+          <t>65,53; 77,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,49; 79,93</t>
+          <t>68,61; 79,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,19; 90,75</t>
+          <t>81,48; 90,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61,83; 70,35</t>
+          <t>62,11; 70,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66,58; 75,05</t>
+          <t>66,76; 75,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,2; 80,28</t>
+          <t>72,83; 80,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,45; 88,3</t>
+          <t>81,15; 88,1</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>71,17; 76,38</t>
+          <t>70,72; 76,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,15; 74,47</t>
+          <t>69,04; 74,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,6</t>
+          <t>65,99; 71,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68,0; 75,21</t>
+          <t>67,77; 75,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71,33; 76,62</t>
+          <t>71,13; 76,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,73; 74,11</t>
+          <t>68,83; 74,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,18; 69,86</t>
+          <t>64,22; 69,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66,64; 73,23</t>
+          <t>66,24; 72,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,97; 75,8</t>
+          <t>71,92; 75,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69,71; 73,46</t>
+          <t>69,93; 73,84</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65,75; 69,67</t>
+          <t>65,38; 69,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67,74; 72,85</t>
+          <t>67,87; 72,87</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>40298</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30823</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34349</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57843</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50335</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38611</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37341</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>57060</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>90633</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69433</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71690</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>114904</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>35034; 44580</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24802; 37109</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28476; 39801</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50887; 63523</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>44799; 54484</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32216; 45315</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30152; 43207</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>49116; 63142</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>83018; 97048</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>60698; 78700</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>62654; 80831</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>105104; 125363</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>59111</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72386</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56531</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100595</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73678</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81536</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63904</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>86304</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>132788</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>153922</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>120434</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>186899</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>50737; 66831</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>63530; 79719</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>48075; 64829</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89161; 114062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>65567; 81017</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>73879; 89119</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>54411; 72387</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>75754; 96337</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>121647; 143995</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>143661; 163982</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>108205; 132253</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>170718; 208312</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>55994</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56858</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36551</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32645</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55215</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>55293</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39944</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>41189</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>111209</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>112151</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76495</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>73834</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>50108; 60453</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51498; 61134</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29468; 43589</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26792; 38459</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>49500; 60172</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>48421; 60215</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>33593; 46534</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>34867; 47210</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>103255; 118109</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>104632; 119473</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>67188; 86570</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>65507; 82387</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>63245</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56540</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55022</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51092</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64533</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60471</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53576</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>58531</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>127778</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>117011</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>108598</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>109623</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>57284; 67172</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49475; 62340</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48217; 61058</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>44409; 56022</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>57945; 69894</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>53227; 66293</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>45984; 60785</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>49409; 66195</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>119724; 135269</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>107214; 126263</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>98692; 118391</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>98514; 118881</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>30406</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24867</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37237</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26098</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29547</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28337</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38973</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>34537</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>59953</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>53204</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>76210</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>60634</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>25591; 34672</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19467; 30898</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32794; 40283</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22120; 29121</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23989; 34448</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>22266; 33429</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>34485; 42383</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>30797; 37250</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>52793; 66959</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>45337; 60881</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>69553; 80813</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>55212; 64581</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>47070</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46819</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37395</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>28557</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>50007</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>42802</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>41529</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>29750</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>97077</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>89621</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>78923</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>58307</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>41521; 50708</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>41503; 50693</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>31648; 42535</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23617; 33553</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>45134; 53829</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>36386; 48306</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>35337; 46537</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>23585; 35875</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>89761; 102425</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>80966; 96792</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>70369; 86925</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>49498; 65945</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>100656</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>107332</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>97433</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>63241</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>102365</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>107436</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>94579</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>87185</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>203021</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>214768</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>192012</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>150426</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>91701; 107432</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>98370; 114964</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>88304; 105387</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>53519; 73273</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>92636; 109518</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>98425; 116182</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>85425; 103726</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>73386; 100801</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>190119; 213375</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>201326; 226807</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>179432; 203440</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>133156; 168077</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>100392</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>115327</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>126078</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>109414</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>106688</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>123470</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>124430</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>135817</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>207080</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>238797</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>250508</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>245231</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>90377; 108602</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>105898; 124676</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>117701; 133691</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>102249; 116053</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>97213; 116079</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>112264; 132443</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>113636; 132283</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>127760; 142532</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>194327; 220429</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>224333; 252012</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>237850; 262199</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>234042; 254093</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>497172</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>510951</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>480594</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>469486</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>530373</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1029540</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1048906</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>974870</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>999859</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>477467; 514381</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>490168; 529356</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>461446; 500446</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>447035; 496594</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>511759; 550048</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>517703; 559539</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>474082; 515200</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>503401; 552053</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1003068; 1055854</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1022475; 1079630</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>939878; 999255</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>963471; 1034488</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IQ23_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,64; 84,8</t>
+          <t>66,89; 85,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,19; 64,62</t>
+          <t>41,29; 63,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,63; 69,37</t>
+          <t>49,48; 69,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,44; 86,68</t>
+          <t>70,11; 87,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,4; 90,48</t>
+          <t>74,96; 90,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,71; 69,92</t>
+          <t>49,16; 69,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,78; 67,03</t>
+          <t>48,15; 69,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,89; 79,56</t>
+          <t>62,55; 80,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,61; 86,05</t>
+          <t>73,82; 85,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,66; 64,38</t>
+          <t>50,25; 65,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51,43; 66,35</t>
+          <t>50,37; 65,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,85; 82,13</t>
+          <t>68,57; 80,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,96; 65,8</t>
+          <t>49,72; 65,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,06; 76,62</t>
+          <t>61,17; 76,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,78; 63,08</t>
+          <t>46,46; 62,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,76; 90,52</t>
+          <t>70,13; 89,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,29; 74,49</t>
+          <t>59,85; 74,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,46; 80,17</t>
+          <t>66,13; 79,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,34; 65,64</t>
+          <t>50,09; 65,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,56; 75,74</t>
+          <t>59,12; 75,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,84; 68,47</t>
+          <t>57,16; 68,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,76; 76,2</t>
+          <t>66,3; 75,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,79; 62,07</t>
+          <t>50,5; 61,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,42; 82,27</t>
+          <t>67,18; 81,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,13; 89,43</t>
+          <t>74,28; 89,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,42; 90,71</t>
+          <t>74,89; 90,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,58; 65,94</t>
+          <t>43,19; 64,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,98; 66,0</t>
+          <t>46,28; 66,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,39; 85,56</t>
+          <t>70,46; 84,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,96; 84,51</t>
+          <t>69,08; 84,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,03; 67,92</t>
+          <t>48,59; 67,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,91; 70,29</t>
+          <t>50,38; 70,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,86; 85,63</t>
+          <t>75,19; 85,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,47; 86,17</t>
+          <t>75,5; 85,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,91; 64,31</t>
+          <t>49,58; 63,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,23; 65,68</t>
+          <t>51,77; 65,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76,52; 89,73</t>
+          <t>76,85; 90,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,62; 80,17</t>
+          <t>63,92; 80,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,65; 79,34</t>
+          <t>62,49; 79,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,01; 85,8</t>
+          <t>68,67; 85,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,25; 88,35</t>
+          <t>73,91; 88,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,26; 81,28</t>
+          <t>65,16; 81,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,64; 74,87</t>
+          <t>56,48; 74,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,56; 86,49</t>
+          <t>63,52; 86,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,76; 87,85</t>
+          <t>77,72; 87,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,29; 79,25</t>
+          <t>67,1; 78,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,41; 74,86</t>
+          <t>62,08; 73,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,46; 83,82</t>
+          <t>69,07; 84,16</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,15; 82,84</t>
+          <t>60,51; 83,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,34; 70,38</t>
+          <t>42,98; 69,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,5; 92,74</t>
+          <t>75,63; 92,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,09; 84,38</t>
+          <t>64,52; 84,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,5; 76,82</t>
+          <t>54,37; 76,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,62; 71,5</t>
+          <t>47,52; 71,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,4; 91,44</t>
+          <t>72,94; 91,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>75,63; 91,48</t>
+          <t>74,55; 91,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,89; 77,24</t>
+          <t>60,61; 76,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,01; 67,16</t>
+          <t>49,01; 66,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,46; 90,0</t>
+          <t>77,49; 90,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,39; 85,84</t>
+          <t>73,12; 86,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,07; 90,46</t>
+          <t>74,33; 90,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,13; 90,55</t>
+          <t>75,38; 90,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,31; 78,37</t>
+          <t>57,99; 78,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51,16; 72,68</t>
+          <t>50,64; 71,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75,56; 90,12</t>
+          <t>75,08; 89,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,4; 80,18</t>
+          <t>60,01; 79,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,2; 80,6</t>
+          <t>59,95; 80,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,98; 63,85</t>
+          <t>42,25; 63,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77,52; 88,46</t>
+          <t>78,46; 88,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,66; 83,28</t>
+          <t>69,92; 82,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,82; 77,6</t>
+          <t>61,77; 77,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48,36; 64,43</t>
+          <t>49,27; 64,38</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,3; 83,53</t>
+          <t>71,89; 83,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,91; 82,88</t>
+          <t>71,09; 82,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,28; 76,72</t>
+          <t>64,02; 76,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,98; 58,85</t>
+          <t>42,5; 58,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,29; 80,73</t>
+          <t>68,82; 81,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,85; 80,09</t>
+          <t>67,54; 79,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,29; 72,0</t>
+          <t>58,86; 71,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,04; 64,61</t>
+          <t>47,76; 64,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,94; 80,74</t>
+          <t>72,38; 81,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70,94; 79,92</t>
+          <t>71,22; 79,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63,75; 72,28</t>
+          <t>63,54; 72,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,47; 59,92</t>
+          <t>48,23; 59,82</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,45; 71,44</t>
+          <t>59,58; 71,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,29; 75,7</t>
+          <t>63,92; 75,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73,13; 83,06</t>
+          <t>72,94; 82,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77,69; 88,17</t>
+          <t>77,04; 87,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,44; 72,17</t>
+          <t>60,72; 72,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,53; 77,31</t>
+          <t>66,48; 76,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,61; 79,86</t>
+          <t>69,75; 80,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,48; 90,9</t>
+          <t>81,68; 90,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62,11; 70,46</t>
+          <t>61,7; 69,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66,76; 75,0</t>
+          <t>66,82; 74,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72,83; 80,28</t>
+          <t>72,89; 80,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,15; 88,1</t>
+          <t>81,29; 88,2</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,19</t>
+          <t>70,92; 76,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,04; 74,56</t>
+          <t>69,23; 74,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,57</t>
+          <t>65,55; 71,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67,77; 75,28</t>
+          <t>67,89; 75,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71,13; 76,45</t>
+          <t>71,44; 76,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,83; 74,39</t>
+          <t>68,73; 74,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,22; 69,79</t>
+          <t>64,03; 69,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66,24; 72,64</t>
+          <t>66,35; 72,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,92; 75,71</t>
+          <t>71,91; 75,67</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69,93; 73,84</t>
+          <t>69,76; 73,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65,38; 69,51</t>
+          <t>65,79; 69,72</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67,87; 72,87</t>
+          <t>68,15; 72,75</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35034; 44580</t>
+          <t>35161; 44813</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24802; 37109</t>
+          <t>23712; 36379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28476; 39801</t>
+          <t>28386; 40103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50887; 63523</t>
+          <t>51377; 64099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44799; 54484</t>
+          <t>45137; 54738</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32216; 45315</t>
+          <t>31858; 45080</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30152; 43207</t>
+          <t>31035; 44568</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49116; 63142</t>
+          <t>49643; 64077</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83018; 97048</t>
+          <t>83254; 96744</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60698; 78700</t>
+          <t>61421; 79510</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62654; 80831</t>
+          <t>61367; 80087</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>105104; 125363</t>
+          <t>104673; 123597</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50737; 66831</t>
+          <t>50493; 66527</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63530; 79719</t>
+          <t>63641; 79447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48075; 64829</t>
+          <t>47748; 64705</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89161; 114062</t>
+          <t>88372; 112654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65567; 81017</t>
+          <t>65086; 81200</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73879; 89119</t>
+          <t>73504; 88764</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54411; 72387</t>
+          <t>55242; 72242</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75754; 96337</t>
+          <t>75201; 96552</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121647; 143995</t>
+          <t>120228; 143487</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143661; 163982</t>
+          <t>142680; 163459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108205; 132253</t>
+          <t>107586; 132057</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>170718; 208312</t>
+          <t>170104; 206366</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50108; 60453</t>
+          <t>50209; 60427</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51498; 61134</t>
+          <t>50468; 61151</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29468; 43589</t>
+          <t>28550; 42852</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26792; 38459</t>
+          <t>26967; 38900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49500; 60172</t>
+          <t>49551; 59598</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48421; 60215</t>
+          <t>49220; 60404</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33593; 46534</t>
+          <t>33292; 46284</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34867; 47210</t>
+          <t>33836; 47094</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>103255; 118109</t>
+          <t>103702; 118569</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104632; 119473</t>
+          <t>104674; 118630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67188; 86570</t>
+          <t>66748; 85806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65507; 82387</t>
+          <t>64935; 82546</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57284; 67172</t>
+          <t>57528; 67442</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49475; 62340</t>
+          <t>49706; 62508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48217; 61058</t>
+          <t>48091; 61180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44409; 56022</t>
+          <t>44837; 55966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57945; 69894</t>
+          <t>58474; 69793</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53227; 66293</t>
+          <t>53150; 66097</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45984; 60785</t>
+          <t>45855; 60160</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49409; 66195</t>
+          <t>48614; 66401</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119724; 135269</t>
+          <t>119675; 134643</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>107214; 126263</t>
+          <t>106915; 125533</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98692; 118391</t>
+          <t>98173; 116957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>98514; 118881</t>
+          <t>97963; 119367</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25591; 34672</t>
+          <t>25325; 34933</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19467; 30898</t>
+          <t>18868; 30304</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32794; 40283</t>
+          <t>32854; 40351</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22120; 29121</t>
+          <t>22266; 29065</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23989; 34448</t>
+          <t>24383; 34452</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22266; 33429</t>
+          <t>22217; 33497</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34485; 42383</t>
+          <t>33810; 42428</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30797; 37250</t>
+          <t>30355; 37445</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52793; 66959</t>
+          <t>52548; 66362</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45337; 60881</t>
+          <t>44428; 60514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69553; 80813</t>
+          <t>69581; 81055</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55212; 64581</t>
+          <t>55007; 65033</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41521; 50708</t>
+          <t>41665; 50596</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41503; 50693</t>
+          <t>42204; 50807</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31648; 42535</t>
+          <t>31475; 42580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23617; 33553</t>
+          <t>23379; 33233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45134; 53829</t>
+          <t>44847; 53740</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36386; 48306</t>
+          <t>36154; 47907</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35337; 46537</t>
+          <t>34615; 46693</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23585; 35875</t>
+          <t>23741; 35865</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>89761; 102425</t>
+          <t>90850; 102987</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80966; 96792</t>
+          <t>81271; 96410</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70369; 86925</t>
+          <t>69185; 86472</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49498; 65945</t>
+          <t>50428; 65896</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>91701; 107432</t>
+          <t>92469; 107967</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>98370; 114964</t>
+          <t>98615; 114896</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88304; 105387</t>
+          <t>87947; 105068</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53519; 73273</t>
+          <t>52912; 72945</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92636; 109518</t>
+          <t>93363; 109969</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>98425; 116182</t>
+          <t>97984; 115752</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85425; 103726</t>
+          <t>84801; 103669</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>73386; 100801</t>
+          <t>74511; 100606</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>190119; 213375</t>
+          <t>191290; 214335</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>201326; 226807</t>
+          <t>202111; 226590</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179432; 203440</t>
+          <t>178835; 204779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>133156; 168077</t>
+          <t>135282; 167804</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>90377; 108602</t>
+          <t>90570; 109160</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>105898; 124676</t>
+          <t>105283; 124775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117701; 133691</t>
+          <t>117401; 133357</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>102249; 116053</t>
+          <t>101404; 115708</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97213; 116079</t>
+          <t>97659; 115890</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>112264; 132443</t>
+          <t>113898; 131903</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>113636; 132283</t>
+          <t>115535; 132575</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>127760; 142532</t>
+          <t>128077; 142283</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>194327; 220429</t>
+          <t>193033; 218653</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>224333; 252012</t>
+          <t>224533; 251132</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>237850; 262199</t>
+          <t>238045; 262180</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>234042; 254093</t>
+          <t>234439; 254372</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>477467; 514381</t>
+          <t>478826; 515681</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>490168; 529356</t>
+          <t>491483; 531483</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>461446; 500446</t>
+          <t>458336; 497620</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>447035; 496594</t>
+          <t>447861; 495758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>511759; 550048</t>
+          <t>513998; 550329</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>517703; 559539</t>
+          <t>516931; 557348</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>474082; 515200</t>
+          <t>472693; 515355</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>503401; 552053</t>
+          <t>504217; 554632</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1003068; 1055854</t>
+          <t>1002908; 1055340</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1022475; 1079630</t>
+          <t>1019954; 1078025</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>939878; 999255</t>
+          <t>945678; 1002204</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>963471; 1034488</t>
+          <t>967512; 1032773</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IQ23_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73,25%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>76,66%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>53,67%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>59,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>78,93%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,93%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,89; 85,25</t>
+          <t>74,08; 90,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,29; 63,35</t>
+          <t>49,12; 69,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,48; 69,9</t>
+          <t>46,18; 67,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70,11; 87,47</t>
+          <t>63,79; 81,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,96; 90,9</t>
+          <t>66,49; 84,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,16; 69,56</t>
+          <t>42,18; 64,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,15; 69,14</t>
+          <t>50,66; 70,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,55; 80,74</t>
+          <t>66,54; 83,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,82; 85,78</t>
+          <t>73,77; 85,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,25; 65,05</t>
+          <t>49,33; 63,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,37; 65,73</t>
+          <t>51,22; 66,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,57; 80,97</t>
+          <t>68,22; 80,59</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>67,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>57,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68,89%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>58,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>69,58%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>55,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>79,83%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>67,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>57,95%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,72; 65,5</t>
+          <t>60,44; 74,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,17; 76,36</t>
+          <t>66,2; 79,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,46; 62,96</t>
+          <t>50,75; 66,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,13; 89,4</t>
+          <t>60,23; 77,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,85; 74,66</t>
+          <t>49,92; 65,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,13; 79,85</t>
+          <t>62,7; 77,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,09; 65,51</t>
+          <t>46,7; 62,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,12; 75,91</t>
+          <t>70,01; 84,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,16; 68,22</t>
+          <t>57,82; 68,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,3; 75,96</t>
+          <t>65,98; 76,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,5; 61,98</t>
+          <t>51,07; 62,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,18; 81,5</t>
+          <t>66,67; 78,23</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>78,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>58,3%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>61,68%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>82,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>84,37%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>55,29%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>58,3%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,28; 89,39</t>
+          <t>70,39; 85,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,89; 90,74</t>
+          <t>68,19; 84,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,19; 64,82</t>
+          <t>48,37; 67,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,28; 66,76</t>
+          <t>52,54; 71,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,46; 84,74</t>
+          <t>74,17; 89,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,08; 84,77</t>
+          <t>75,98; 90,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,59; 67,55</t>
+          <t>44,17; 64,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,38; 70,12</t>
+          <t>46,59; 66,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75,19; 85,97</t>
+          <t>75,54; 85,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,5; 85,56</t>
+          <t>75,34; 85,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,58; 63,74</t>
+          <t>49,68; 64,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,77; 65,81</t>
+          <t>51,43; 65,59</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>74,14%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65,99%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76,48%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>84,48%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>72,71%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>71,49%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,99%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76,85; 90,09</t>
+          <t>72,62; 88,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,92; 80,38</t>
+          <t>65,33; 82,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,49; 79,49</t>
+          <t>56,16; 74,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,67; 85,71</t>
+          <t>64,59; 87,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,91; 88,22</t>
+          <t>77,79; 90,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,16; 81,04</t>
+          <t>64,55; 80,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,48; 74,1</t>
+          <t>62,37; 79,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,52; 86,76</t>
+          <t>69,21; 86,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,72; 87,45</t>
+          <t>78,12; 87,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,1; 78,79</t>
+          <t>67,4; 78,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,08; 73,96</t>
+          <t>62,68; 74,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,07; 84,16</t>
+          <t>70,21; 83,95</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>65,89%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>60,61%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>84,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>85,24%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>72,65%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>56,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>85,72%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>75,62%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>65,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>60,61%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>84,09%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,51; 83,47</t>
+          <t>53,55; 76,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,98; 69,03</t>
+          <t>48,2; 71,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,63; 92,89</t>
+          <t>73,6; 91,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,52; 84,21</t>
+          <t>76,19; 91,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,37; 76,83</t>
+          <t>61,62; 82,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,52; 71,65</t>
+          <t>42,89; 67,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,94; 91,54</t>
+          <t>75,58; 93,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>74,55; 91,96</t>
+          <t>64,07; 83,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,61; 76,55</t>
+          <t>60,35; 75,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,01; 66,75</t>
+          <t>50,36; 67,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,49; 90,27</t>
+          <t>77,21; 90,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,12; 86,44</t>
+          <t>74,08; 86,68</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71,05%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55,73%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>83,97%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>83,63%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>68,9%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>83,72%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,33; 90,26</t>
+          <t>75,24; 90,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,38; 90,75</t>
+          <t>60,72; 79,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,99; 78,46</t>
+          <t>60,26; 80,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,64; 71,99</t>
+          <t>44,79; 65,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75,08; 89,97</t>
+          <t>74,76; 91,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,01; 79,52</t>
+          <t>74,39; 89,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,95; 80,87</t>
+          <t>58,09; 79,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,25; 63,83</t>
+          <t>53,15; 73,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78,46; 88,94</t>
+          <t>77,9; 88,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,92; 82,95</t>
+          <t>69,71; 82,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61,77; 77,2</t>
+          <t>63,28; 76,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,27; 64,38</t>
+          <t>52,11; 67,32</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75,46%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74,06%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>65,65%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55,21%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>78,26%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>77,37%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>70,93%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50,79%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>75,46%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,65%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,89; 83,94</t>
+          <t>69,62; 81,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,09; 82,83</t>
+          <t>67,78; 80,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,02; 76,48</t>
+          <t>58,48; 71,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,5; 58,59</t>
+          <t>45,78; 62,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,82; 81,06</t>
+          <t>72,21; 83,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,54; 79,79</t>
+          <t>71,07; 82,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,86; 71,96</t>
+          <t>64,92; 77,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,76; 64,49</t>
+          <t>43,81; 58,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,38; 81,1</t>
+          <t>72,3; 80,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71,22; 79,84</t>
+          <t>70,98; 79,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63,54; 72,76</t>
+          <t>63,75; 72,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,23; 59,82</t>
+          <t>47,71; 59,19</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>66,33%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>72,07%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>75,12%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>66,04%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>70,02%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>78,33%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>75,12%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,58; 71,8</t>
+          <t>60,48; 72,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63,92; 75,76</t>
+          <t>65,91; 77,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,94; 82,85</t>
+          <t>69,49; 79,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77,04; 87,91</t>
+          <t>82,46; 91,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,72; 72,05</t>
+          <t>59,27; 71,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,48; 76,99</t>
+          <t>64,22; 75,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,75; 80,04</t>
+          <t>72,99; 82,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,68; 90,74</t>
+          <t>79,26; 89,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61,7; 69,89</t>
+          <t>61,83; 70,35</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66,82; 74,74</t>
+          <t>66,58; 75,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72,89; 80,28</t>
+          <t>73,2; 80,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,29; 88,2</t>
+          <t>82,85; 89,43</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>73,99%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>73,99%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,92; 76,38</t>
+          <t>71,33; 76,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,23; 74,86</t>
+          <t>68,73; 74,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65,55; 71,16</t>
+          <t>64,18; 69,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67,89; 75,15</t>
+          <t>67,79; 74,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71,44; 76,49</t>
+          <t>71,17; 76,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,73; 74,1</t>
+          <t>69,15; 74,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,03; 69,81</t>
+          <t>65,99; 71,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66,35; 72,98</t>
+          <t>68,09; 73,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,91; 75,67</t>
+          <t>71,97; 75,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69,76; 73,73</t>
+          <t>69,71; 73,46</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65,79; 69,72</t>
+          <t>65,75; 69,67</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>68,15; 72,75</t>
+          <t>68,42; 73,08</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50335</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38611</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37341</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>46987</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>40298</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>30823</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>34349</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57843</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>50335</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38611</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37341</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57060</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>114904</t>
+          <t>89871</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35161; 44813</t>
+          <t>44610; 54590</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23712; 36379</t>
+          <t>31832; 44901</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28386; 40103</t>
+          <t>29771; 43707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51377; 64099</t>
+          <t>40917; 52166</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45137; 54738</t>
+          <t>34952; 44406</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31858; 45080</t>
+          <t>24220; 36881</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31035; 44568</t>
+          <t>29064; 40284</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49643; 64077</t>
+          <t>37582; 47252</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83254; 96744</t>
+          <t>83203; 96823</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61421; 79510</t>
+          <t>60297; 77632</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61367; 80087</t>
+          <t>62399; 80492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>104673; 123597</t>
+          <t>82295; 97214</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>103</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73678</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81536</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63904</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79593</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>59111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>72386</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>56531</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>100595</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73678</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81536</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63904</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86304</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>186899</t>
+          <t>157189</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50493; 66527</t>
+          <t>65734; 80953</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63641; 79447</t>
+          <t>73587; 88680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47748; 64705</t>
+          <t>55969; 72848</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88372; 112654</t>
+          <t>69589; 89260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65086; 81200</t>
+          <t>50704; 66763</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73504; 88764</t>
+          <t>65232; 80120</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55242; 72242</t>
+          <t>47993; 64447</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75201; 96552</t>
+          <t>69897; 83972</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120228; 143487</t>
+          <t>121603; 144220</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142680; 163459</t>
+          <t>141985; 164859</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107586; 132057</t>
+          <t>108806; 132164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>170104; 206366</t>
+          <t>143577; 168480</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>55215</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55293</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39944</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36622</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>55994</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>56858</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>36551</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32645</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55215</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55293</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39944</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41189</t>
+          <t>31787</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73834</t>
+          <t>68410</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50209; 60427</t>
+          <t>49506; 60245</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50468; 61151</t>
+          <t>48586; 60182</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28550; 42852</t>
+          <t>33139; 46422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26967; 38900</t>
+          <t>31198; 42302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49551; 59598</t>
+          <t>50137; 60804</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49220; 60404</t>
+          <t>51202; 61074</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33292; 46284</t>
+          <t>29201; 42814</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33836; 47094</t>
+          <t>26352; 37533</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>103702; 118569</t>
+          <t>104192; 118182</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104674; 118630</t>
+          <t>104457; 118881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66748; 85806</t>
+          <t>66875; 87031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64935; 82546</t>
+          <t>59625; 76040</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64533</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60471</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53576</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53962</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>63245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>56540</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>55022</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51092</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64533</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60471</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53576</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>52241</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>106203</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57528; 67442</t>
+          <t>57449; 69628</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49706; 62508</t>
+          <t>53290; 67178</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48091; 61180</t>
+          <t>45591; 60314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44837; 55966</t>
+          <t>45571; 61484</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58474; 69793</t>
+          <t>58237; 67803</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53150; 66097</t>
+          <t>50195; 62568</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45855; 60160</t>
+          <t>48003; 61021</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48614; 66401</t>
+          <t>45761; 57197</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119675; 134643</t>
+          <t>120289; 134827</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>106915; 125533</t>
+          <t>107386; 125502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98173; 116957</t>
+          <t>99133; 118188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>97963; 119367</t>
+          <t>95967; 114733</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>29547</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28337</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38973</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33738</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>30406</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>24867</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>37237</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26098</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29547</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28337</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38973</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60634</t>
+          <t>60707</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25325; 34933</t>
+          <t>24015; 34442</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18868; 30304</t>
+          <t>22534; 33482</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32854; 40351</t>
+          <t>34114; 42521</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22266; 29065</t>
+          <t>30154; 36319</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24383; 34452</t>
+          <t>25788; 34604</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22217; 33497</t>
+          <t>18829; 29685</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33810; 42428</t>
+          <t>32831; 40498</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30355; 37445</t>
+          <t>22813; 29896</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52548; 66362</t>
+          <t>52323; 65835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44428; 60514</t>
+          <t>45655; 61223</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69581; 81055</t>
+          <t>69322; 80969</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55007; 65033</t>
+          <t>55695; 65171</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>50007</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>42802</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>41529</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27277</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>47070</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>46819</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>37395</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28557</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>50007</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42802</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>41529</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58307</t>
+          <t>56605</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41665; 50596</t>
+          <t>44940; 54092</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42204; 50807</t>
+          <t>36579; 48074</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31475; 42580</t>
+          <t>34791; 46632</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23379; 33233</t>
+          <t>21919; 32287</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44847; 53740</t>
+          <t>41907; 51184</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36154; 47907</t>
+          <t>41647; 50333</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34615; 46693</t>
+          <t>31528; 42979</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23741; 35865</t>
+          <t>24326; 33696</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>90850; 102987</t>
+          <t>90201; 102858</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81271; 96410</t>
+          <t>81026; 95976</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69185; 86472</t>
+          <t>70880; 86187</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50428; 65896</t>
+          <t>49351; 63761</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>86</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>102365</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>107436</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>94579</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>78056</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>100656</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>107332</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>97433</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>63241</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>102365</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>107436</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>94579</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>87185</t>
+          <t>62816</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>150426</t>
+          <t>140872</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>92469; 107967</t>
+          <t>94444; 110459</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>98615; 114896</t>
+          <t>98327; 116571</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87947; 105068</t>
+          <t>84247; 103091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52912; 72945</t>
+          <t>64720; 88776</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>93363; 109969</t>
+          <t>92880; 107354</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>97984; 115752</t>
+          <t>98590; 114291</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84801; 103669</t>
+          <t>89189; 106021</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>74511; 100606</t>
+          <t>53681; 72107</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>191290; 214335</t>
+          <t>191061; 213490</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>202111; 226590</t>
+          <t>201427; 225956</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178835; 204779</t>
+          <t>179416; 204330</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>135282; 167804</t>
+          <t>125895; 156201</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>154</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>106688</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>123470</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>124430</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>139795</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>100392</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>115327</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>126078</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>109414</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>106688</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>123470</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>124430</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>135817</t>
+          <t>119113</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>245231</t>
+          <t>258908</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>90570; 109160</t>
+          <t>97277; 115849</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>105283; 124775</t>
+          <t>112907; 133013</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117401; 133357</t>
+          <t>115107; 132392</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>101404; 115708</t>
+          <t>131462; 146035</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97659; 115890</t>
+          <t>90099; 108605</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>113898; 131903</t>
+          <t>105770; 124261</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>115535; 132575</t>
+          <t>117481; 133569</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>128077; 142283</t>
+          <t>111360; 125472</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>193033; 218653</t>
+          <t>193432; 220083</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>224533; 251132</t>
+          <t>223733; 252180</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>238045; 262180</t>
+          <t>239072; 262199</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>234439; 254372</t>
+          <t>248473; 268205</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>630</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>532368</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>537955</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442733</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>478826; 515681</t>
+          <t>513235; 551237</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>491483; 531483</t>
+          <t>516946; 557406</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>458336; 497620</t>
+          <t>473777; 515717</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>447861; 495758</t>
+          <t>473783; 518880</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>513998; 550329</t>
+          <t>480522; 515664</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>516931; 557348</t>
+          <t>490900; 528676</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>472693; 515355</t>
+          <t>461458; 500683</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>504217; 554632</t>
+          <t>424474; 460390</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1002908; 1055340</t>
+          <t>1003723; 1057093</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1019954; 1078025</t>
+          <t>1019157; 1074094</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>945678; 1002204</t>
+          <t>945109; 1001563</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>967512; 1032773</t>
+          <t>904712; 966284</t>
         </is>
       </c>
     </row>
